--- a/Інтелектуальний аналіз даних/Horetskyi_lab5-6-7-8.xlsx
+++ b/Інтелектуальний аналіз даних/Horetskyi_lab5-6-7-8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\edu\education\Інтелектуальний аналіз даних\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\education\Інтелектуальний аналіз даних\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A4C7A2E-F2E6-4D81-9B58-20B4BEF910CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435496A4-E5B8-4F2A-996A-0B102D6E4774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Приклад 2.1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
   <si>
     <t>Проект</t>
   </si>
@@ -666,13 +666,22 @@
       </rPr>
       <t>, адже він забезпечує менший відсоток браку та менші загальні витрати.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Завдання 1</t>
+  </si>
+  <si>
+    <t>Завдання 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -700,6 +709,15 @@
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -802,7 +820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -868,6 +886,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -889,15 +913,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -910,6 +931,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>104774</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>92061</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F88DA33B-8D8F-4E28-835F-4645B7E50109}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="590550" y="723899"/>
+          <a:ext cx="5581650" cy="3606787"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>103480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>8609</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F44634B5-FA72-4927-95CE-D15E38F97035}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6705600" y="722605"/>
+          <a:ext cx="6867525" cy="4286629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1198,14 +1312,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1219,7 +1333,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -1234,7 +1348,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -1249,7 +1363,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>6</v>
       </c>
@@ -1264,13 +1378,13 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -1286,15 +1400,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.21875" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" customWidth="1"/>
-    <col min="4" max="4" width="9.109375" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
@@ -1308,7 +1422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>12</v>
       </c>
@@ -1323,7 +1437,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
@@ -1338,13 +1452,13 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
         <v>14</v>
       </c>
@@ -1355,7 +1469,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
         <v>16</v>
       </c>
@@ -1365,7 +1479,7 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
         <v>15</v>
       </c>
@@ -1389,15 +1503,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" customWidth="1"/>
-    <col min="4" max="4" width="9.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -1411,7 +1525,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
@@ -1426,7 +1540,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -1441,7 +1555,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1456,13 +1570,13 @@
         <v>70000</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -1472,19 +1586,19 @@
       </c>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>60</v>
       </c>
@@ -1492,7 +1606,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
@@ -1521,14 +1635,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:T25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.21875" customWidth="1"/>
-    <col min="3" max="3" width="11.21875" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="15" max="15" width="23.5703125" customWidth="1"/>
+    <col min="20" max="20" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -1562,7 +1678,7 @@
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
     </row>
-    <row r="2" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2">
         <v>0.8</v>
@@ -1594,7 +1710,7 @@
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
     </row>
-    <row r="3" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1616,8 +1732,8 @@
       <c r="S3" s="3"/>
       <c r="T3" s="3"/>
     </row>
-    <row r="4" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="30"/>
@@ -1640,7 +1756,7 @@
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
     </row>
-    <row r="5" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1662,7 +1778,7 @@
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
     </row>
-    <row r="6" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
@@ -1692,7 +1808,7 @@
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
     </row>
-    <row r="7" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -1725,7 +1841,7 @@
       <c r="S7" s="16"/>
       <c r="T7" s="17"/>
     </row>
-    <row r="8" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1756,7 +1872,7 @@
       <c r="S8" s="7"/>
       <c r="T8" s="8"/>
     </row>
-    <row r="9" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -1770,11 +1886,11 @@
         <v>70000</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -1788,7 +1904,7 @@
       <c r="S9" s="7"/>
       <c r="T9" s="8"/>
     </row>
-    <row r="10" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
@@ -1815,22 +1931,22 @@
       <c r="S10" s="7"/>
       <c r="T10" s="8"/>
     </row>
-    <row r="11" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
       <c r="N11" s="19"/>
       <c r="O11" s="19"/>
       <c r="P11" s="7"/>
@@ -1839,13 +1955,13 @@
       <c r="S11" s="7"/>
       <c r="T11" s="8"/>
     </row>
-    <row r="12" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
       <c r="E12" s="3"/>
       <c r="F12" s="20"/>
       <c r="G12" s="21"/>
@@ -1863,31 +1979,31 @@
       <c r="S12" s="7"/>
       <c r="T12" s="8"/>
     </row>
-    <row r="13" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="33" t="s">
+      <c r="F13" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="8"/>
     </row>
-    <row r="14" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -1917,7 +2033,7 @@
       <c r="S14" s="7"/>
       <c r="T14" s="8"/>
     </row>
-    <row r="15" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -1932,25 +2048,25 @@
         <v>65000</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="33" t="s">
+      <c r="F15" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
-      <c r="Q15" s="34"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="8"/>
     </row>
-    <row r="16" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -1981,7 +2097,7 @@
       <c r="S16" s="7"/>
       <c r="T16" s="8"/>
     </row>
-    <row r="17" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -1996,25 +2112,25 @@
         <v>70000</v>
       </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
-      <c r="R17" s="36"/>
-      <c r="S17" s="36"/>
-      <c r="T17" s="37"/>
-    </row>
-    <row r="18" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="38"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="39"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>35</v>
       </c>
@@ -2041,7 +2157,7 @@
       <c r="S18" s="7"/>
       <c r="T18" s="8"/>
     </row>
-    <row r="19" spans="1:20" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2065,13 +2181,13 @@
       <c r="S19" s="9"/>
       <c r="T19" s="11"/>
     </row>
-    <row r="20" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="38" t="s">
+    <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -2089,7 +2205,7 @@
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="1"/>
       <c r="C21" s="2"/>
@@ -2111,12 +2227,12 @@
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
     </row>
-    <row r="22" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="39" t="s">
+    <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
       <c r="D22" s="1" t="s">
         <v>39</v>
       </c>
@@ -2137,7 +2253,7 @@
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
     </row>
-    <row r="23" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>40</v>
       </c>
@@ -2164,7 +2280,7 @@
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
     </row>
-    <row r="24" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
         <v>41</v>
       </c>
@@ -2191,7 +2307,7 @@
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
     </row>
-    <row r="25" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
         <v>42</v>
       </c>
@@ -2219,6 +2335,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F13:O13"/>
+    <mergeCell ref="F15:Q15"/>
+    <mergeCell ref="F17:T17"/>
+    <mergeCell ref="F11:M11"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A4:D4"/>
@@ -2226,11 +2347,6 @@
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F13:O13"/>
-    <mergeCell ref="F15:Q15"/>
-    <mergeCell ref="F17:T17"/>
-    <mergeCell ref="F11:M11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2239,25 +2355,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.21875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" style="3" customWidth="1"/>
-    <col min="4" max="15" width="8.88671875" style="3"/>
-    <col min="16" max="16" width="16.77734375" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="11.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="3" customWidth="1"/>
+    <col min="4" max="15" width="8.85546875" style="3"/>
+    <col min="16" max="16" width="16.7109375" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2276,7 +2392,7 @@
       <c r="O2" s="16"/>
       <c r="P2" s="17"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -2299,7 +2415,7 @@
       <c r="O3" s="7"/>
       <c r="P3" s="8"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
         <v>0.01</v>
       </c>
@@ -2324,7 +2440,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="8"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="25">
         <v>0.02</v>
       </c>
@@ -2347,7 +2463,7 @@
       <c r="O5" s="7"/>
       <c r="P5" s="8"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <v>0.03</v>
       </c>
@@ -2372,7 +2488,7 @@
       <c r="O6" s="7"/>
       <c r="P6" s="8"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="25">
         <v>0.04</v>
       </c>
@@ -2395,7 +2511,7 @@
       <c r="O7" s="7"/>
       <c r="P7" s="8"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="25">
         <v>0.05</v>
       </c>
@@ -2420,7 +2536,7 @@
       <c r="O8" s="7"/>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2437,12 +2553,12 @@
       <c r="O9" s="7"/>
       <c r="P9" s="8"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="38" t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="2"/>
       <c r="F10" s="18"/>
       <c r="G10" s="7"/>
@@ -2456,7 +2572,7 @@
       <c r="O10" s="7"/>
       <c r="P10" s="8"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2473,11 +2589,11 @@
       <c r="O11" s="7"/>
       <c r="P11" s="8"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="38" t="s">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="38"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="1" t="s">
         <v>58</v>
       </c>
@@ -2496,7 +2612,7 @@
       <c r="O12" s="7"/>
       <c r="P12" s="8"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
         <v>48</v>
       </c>
@@ -2517,7 +2633,7 @@
       <c r="O13" s="7"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
         <v>49</v>
       </c>
@@ -2540,7 +2656,7 @@
       <c r="O14" s="7"/>
       <c r="P14" s="8"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
         <v>59</v>
       </c>
@@ -2561,7 +2677,7 @@
       <c r="O15" s="7"/>
       <c r="P15" s="8"/>
     </row>
-    <row r="16" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2580,31 +2696,31 @@
       <c r="O16" s="9"/>
       <c r="P16" s="11"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="38" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="38" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="38"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
         <v>53</v>
       </c>
@@ -2615,7 +2731,7 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
         <v>54</v>
       </c>
@@ -2626,7 +2742,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>55</v>
       </c>
@@ -2637,7 +2753,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>56</v>
       </c>
@@ -2647,8 +2763,11 @@
         <v>3673900</v>
       </c>
       <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="J23" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="30" t="s">
         <v>57</v>
       </c>
@@ -2661,12 +2780,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A12:B12"/>
@@ -2674,6 +2787,12 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2681,9 +2800,42 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="B3:V3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:22" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B3" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="L3" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="L3:V3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Інтелектуальний аналіз даних/Horetskyi_lab5-6-7-8.xlsx
+++ b/Інтелектуальний аналіз даних/Horetskyi_lab5-6-7-8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\education\Інтелектуальний аналіз даних\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435496A4-E5B8-4F2A-996A-0B102D6E4774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B75B5D-F008-4828-B89C-1B04579CDAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Приклад 2.1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>Проект</t>
   </si>
@@ -675,6 +675,9 @@
   </si>
   <si>
     <t>Завдання 2</t>
+  </si>
+  <si>
+    <t>Завдання 3</t>
   </si>
 </sst>
 </file>
@@ -886,12 +889,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -912,6 +909,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -938,15 +941,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
+      <xdr:colOff>422460</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>104774</xdr:rowOff>
+      <xdr:rowOff>93568</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>92061</xdr:rowOff>
+      <xdr:colOff>123263</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>30509</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -969,8 +972,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="590550" y="723899"/>
-          <a:ext cx="5581650" cy="3606787"/>
+          <a:off x="422460" y="709892"/>
+          <a:ext cx="5751979" cy="3746941"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1015,6 +1018,50 @@
         <a:xfrm>
           <a:off x="6705600" y="722605"/>
           <a:ext cx="6867525" cy="4286629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>89647</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>89646</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>105971</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23126113-4C64-4EA5-BBFB-A814BECC5501}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14007353" y="705970"/>
+          <a:ext cx="6566647" cy="5350325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1733,7 +1780,7 @@
       <c r="T3" s="3"/>
     </row>
     <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="38" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="30"/>
@@ -1886,11 +1933,11 @@
         <v>70000</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -1937,16 +1984,16 @@
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="19"/>
       <c r="O11" s="19"/>
       <c r="P11" s="7"/>
@@ -1956,12 +2003,12 @@
       <c r="T11" s="8"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
       <c r="E12" s="3"/>
       <c r="F12" s="20"/>
       <c r="G12" s="21"/>
@@ -1985,18 +2032,18 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="36"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -2048,20 +2095,20 @@
         <v>65000</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="36"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="8"/>
@@ -2112,23 +2159,23 @@
         <v>70000</v>
       </c>
       <c r="E17" s="3"/>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
-      <c r="T17" s="39"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
+      <c r="T17" s="37"/>
     </row>
     <row r="18" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
@@ -2182,12 +2229,12 @@
       <c r="T19" s="11"/>
     </row>
     <row r="20" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -2228,11 +2275,11 @@
       <c r="T21" s="3"/>
     </row>
     <row r="22" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
       <c r="D22" s="1" t="s">
         <v>39</v>
       </c>
@@ -2335,11 +2382,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F13:O13"/>
-    <mergeCell ref="F15:Q15"/>
-    <mergeCell ref="F17:T17"/>
-    <mergeCell ref="F11:M11"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A4:D4"/>
@@ -2347,6 +2389,11 @@
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F13:O13"/>
+    <mergeCell ref="F15:Q15"/>
+    <mergeCell ref="F17:T17"/>
+    <mergeCell ref="F11:M11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2361,16 +2408,16 @@
     <col min="2" max="2" width="16.5703125" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.7109375" style="3" customWidth="1"/>
     <col min="4" max="15" width="8.85546875" style="3"/>
-    <col min="16" max="16" width="16.7109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" style="3" customWidth="1"/>
     <col min="17" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
       <c r="D1" s="2"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -2554,11 +2601,11 @@
       <c r="P9" s="8"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="2"/>
       <c r="F10" s="18"/>
       <c r="G10" s="7"/>
@@ -2590,10 +2637,10 @@
       <c r="P11" s="8"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="31"/>
+      <c r="B12" s="38"/>
       <c r="C12" s="1" t="s">
         <v>58</v>
       </c>
@@ -2697,11 +2744,11 @@
       <c r="P16" s="11"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2711,10 +2758,10 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="31"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="1" t="s">
         <v>52</v>
       </c>
@@ -2780,6 +2827,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A12:B12"/>
@@ -2787,12 +2840,6 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2800,10 +2847,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B3:V3"/>
+  <dimension ref="B3:AH3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="2:22" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:34" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B3" s="40" t="s">
         <v>75</v>
       </c>
@@ -2828,11 +2875,25 @@
       <c r="T3" s="40"/>
       <c r="U3" s="40"/>
       <c r="V3" s="40"/>
+      <c r="X3" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="40"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40"/>
+      <c r="AE3" s="40"/>
+      <c r="AF3" s="40"/>
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="L3:V3"/>
+    <mergeCell ref="X3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
